--- a/Unecont/assets/templates/report-layout-example.xlsx
+++ b/Unecont/assets/templates/report-layout-example.xlsx
@@ -73,7 +73,7 @@
     <t>DESCRIÇÃO DO SERVIÇO</t>
   </si>
   <si>
-    <t>QUAL SERVIÇO CONTRATO</t>
+    <t>QUAL SERVIÇO CONTRATADO</t>
   </si>
   <si>
     <t>Serviço Dentro do Município</t>
@@ -145,7 +145,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="00\.00-0-00"/>
+    <numFmt numFmtId="165" formatCode="00.00-0-00"/>
     <numFmt numFmtId="166" formatCode="_-R$* #,##0.00_-;-R$* #,##0.00_-_-R$* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
@@ -589,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -615,7 +615,7 @@
     <col min="25" max="25" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -770,6 +770,6 @@
     <hyperlink ref="Y2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>